--- a/questionnaire_templates/003_car_rental_system_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/003_car_rental_system_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -793,8 +793,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -822,12 +822,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly', 'value': 'weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly', 'value': 'monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly',_'value':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly', 'value': 'quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'annually',_'value':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Annually', 'value': 'annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'business',_'value':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Business', 'value': 'business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'leisure/vacation',_'value':_'leisure'}</t>
+          <t>leisure/vacation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Leisure/Vacation', 'value': 'leisure'}</t>
+          <t>Leisure/Vacation</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'insurance_replacement',_'value':_'insurance'}</t>
+          <t>insurance_replacement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Insurance Replacement', 'value': 'insurance'}</t>
+          <t>Insurance Replacement</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'special_occasion',_'value':_'special'}</t>
+          <t>special_occasion</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Special Occasion', 'value': 'special'}</t>
+          <t>Special Occasion</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'rental_price',_'value':_'price'}</t>
+          <t>rental_price</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Rental Price', 'value': 'price'}</t>
+          <t>Rental Price</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'vehicle_type_variety',_'value':_'vehicle'}</t>
+          <t>vehicle_type_variety</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Vehicle Type Variety', 'value': 'vehicle'}</t>
+          <t>Vehicle Type Variety</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'pickup/dropoff_locations',_'value':_'location'}</t>
+          <t>pickup/dropoff_locations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Pickup/Dropoff Locations', 'value': 'location'}</t>
+          <t>Pickup/Dropoff Locations</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'customer_service_reputation',_'value':_'service'}</t>
+          <t>customer_service_reputation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Customer Service Reputation', 'value': 'service'}</t>
+          <t>Customer Service Reputation</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'loyalty_program',_'value':_'loyalty'}</t>
+          <t>loyalty_program</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Loyalty Program', 'value': 'loyalty'}</t>
+          <t>Loyalty Program</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'online_website',_'value':_'website'}</t>
+          <t>online_website</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Online Website', 'value': 'website'}</t>
+          <t>Online Website</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'mobile_application',_'value':_'app'}</t>
+          <t>mobile_application</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Mobile Application', 'value': 'app'}</t>
+          <t>Mobile Application</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'telephone_hotline',_'value':_'phone'}</t>
+          <t>telephone_hotline</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Telephone Hotline', 'value': 'phone'}</t>
+          <t>Telephone Hotline</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'in-person/walk-in',_'value':_'in_person'}</t>
+          <t>in-person/walk-in</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'In-Person/Walk-in', 'value': 'in_person'}</t>
+          <t>In-Person/Walk-in</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'contactless_pickup',_'value':_'contactless'}</t>
+          <t>contactless_pickup</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Contactless Pickup', 'value': 'contactless'}</t>
+          <t>Contactless Pickup</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'real-time_vehicle_tracking',_'value':_'tracking'}</t>
+          <t>real-time_vehicle_tracking</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Real-time Vehicle Tracking', 'value': 'tracking'}</t>
+          <t>Real-time Vehicle Tracking</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'mobile_payment_integration',_'value':_'mobile_pay'}</t>
+          <t>mobile_payment_integration</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Mobile Payment Integration', 'value': 'mobile_pay'}</t>
+          <t>Mobile Payment Integration</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'24/7_virtual_support',_'value':_'virtual_support'}</t>
+          <t>24/7_virtual_support</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': '24/7 Virtual Support', 'value': 'virtual_support'}</t>
+          <t>24/7 Virtual Support</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_please',_'value':_true}</t>
+          <t>yes,_please</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, please', 'value': True}</t>
+          <t>Yes, please</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'no,_thanks',_'value':_false}</t>
+          <t>no,_thanks</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'No, thanks', 'value': False}</t>
+          <t>No, thanks</t>
         </is>
       </c>
     </row>
